--- a/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -15,12 +15,13 @@
     <sheet name="Include #5" r:id="rId9" sheetId="7"/>
     <sheet name="Include #6" r:id="rId10" sheetId="8"/>
     <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2026.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -95,6 +96,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define Alpha-ID codes allowed for diagnosis coding in the MII Diagnosis module.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -362,22 +366,64 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -396,28 +442,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -436,28 +482,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -476,28 +522,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -516,28 +562,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -556,28 +602,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -596,28 +642,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -636,28 +682,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -676,28 +722,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -92,7 +92,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Enthaelt Alpha-ID-Codes der Versionen 2018 bis 2025</t>
+    <t>Enthaelt Alpha-ID-Codes der aller verfügbarer Versionen</t>
   </si>
   <si>
     <t>Purpose</t>
